--- a/JPS_LE_Sales_Gen_FY2026-28.xlsx
+++ b/JPS_LE_Sales_Gen_FY2026-28.xlsx
@@ -946,43 +946,43 @@
         <v>693810000</v>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>47473607</v>
+        <v>47935473</v>
       </c>
       <c r="AC7" s="7" t="n">
-        <v>44782732</v>
+        <v>45218419</v>
       </c>
       <c r="AD7" s="7" t="n">
-        <v>53130660</v>
+        <v>53647563</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>50653862</v>
+        <v>51146668</v>
       </c>
       <c r="AF7" s="7" t="n">
-        <v>59317664</v>
+        <v>59894760</v>
       </c>
       <c r="AG7" s="7" t="n">
-        <v>58955580</v>
+        <v>59529153</v>
       </c>
       <c r="AH7" s="7" t="n">
-        <v>64858838</v>
+        <v>65489843</v>
       </c>
       <c r="AI7" s="7" t="n">
-        <v>65838403</v>
+        <v>66478938</v>
       </c>
       <c r="AJ7" s="7" t="n">
-        <v>63825874</v>
+        <v>64446830</v>
       </c>
       <c r="AK7" s="7" t="n">
-        <v>65839285</v>
+        <v>66479829</v>
       </c>
       <c r="AL7" s="7" t="n">
-        <v>64573575</v>
+        <v>65201804</v>
       </c>
       <c r="AM7" s="7" t="n">
-        <v>63809920</v>
+        <v>64430721</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>703060000</v>
+        <v>709900000</v>
       </c>
     </row>
     <row r="8">
@@ -1070,43 +1070,43 @@
         <v>827110000</v>
       </c>
       <c r="AB8" s="7" t="n">
-        <v>59832339</v>
+        <v>60132494</v>
       </c>
       <c r="AC8" s="7" t="n">
-        <v>56425292</v>
+        <v>56708355</v>
       </c>
       <c r="AD8" s="7" t="n">
-        <v>65895050</v>
+        <v>66225620</v>
       </c>
       <c r="AE8" s="7" t="n">
-        <v>63660656</v>
+        <v>63980016</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>70406810</v>
+        <v>70760013</v>
       </c>
       <c r="AG8" s="7" t="n">
-        <v>68781729</v>
+        <v>69126780</v>
       </c>
       <c r="AH8" s="7" t="n">
-        <v>74920590</v>
+        <v>75296436</v>
       </c>
       <c r="AI8" s="7" t="n">
-        <v>73093108</v>
+        <v>73459787</v>
       </c>
       <c r="AJ8" s="7" t="n">
-        <v>70253101</v>
+        <v>70605532</v>
       </c>
       <c r="AK8" s="7" t="n">
-        <v>72460508</v>
+        <v>72824014</v>
       </c>
       <c r="AL8" s="7" t="n">
-        <v>71922202</v>
+        <v>72283007</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>71628615</v>
+        <v>71987947</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>819280000</v>
+        <v>823390000</v>
       </c>
     </row>
     <row r="9">
@@ -1566,43 +1566,43 @@
         <v>3406350000</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>245569748</v>
+        <v>246331768</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>231516203</v>
+        <v>232234952</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>269711939</v>
+        <v>270559411</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>261475751</v>
+        <v>262287917</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>293049060</v>
+        <v>293979359</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>291102858</v>
+        <v>292021482</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>317938347</v>
+        <v>318945199</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>315239768</v>
+        <v>316246982</v>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>305743478</v>
+        <v>306716866</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>314776125</v>
+        <v>315780174</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>310264185</v>
+        <v>311253220</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>307902539</v>
+        <v>308882671</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>3464290000</v>
+        <v>3475240000</v>
       </c>
     </row>
     <row r="13">
@@ -1711,7 +1711,7 @@
         <v>0.25364529</v>
       </c>
       <c r="AK13" s="10" t="n">
-        <v>0.29109529</v>
+        <v>0.2910952900000001</v>
       </c>
       <c r="AL13" s="10" t="n">
         <v>0.22869529</v>
@@ -1763,40 +1763,40 @@
         <v>0.2710000033313201</v>
       </c>
       <c r="AB14" s="10" t="n">
-        <v>0.2710084242800463</v>
+        <v>0.2710099090349518</v>
       </c>
       <c r="AC14" s="10" t="n">
-        <v>0.2709601743227563</v>
+        <v>0.2709531031715005</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.2709908497122918</v>
+        <v>0.2709894891292186</v>
       </c>
       <c r="AE14" s="10" t="n">
-        <v>0.2709946504793775</v>
+        <v>0.2709939796164094</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>0.2710487959717811</v>
+        <v>0.2710583843781971</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.2710408190790013</v>
+        <v>0.2710488519537005</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.2710256565258747</v>
+        <v>0.2710307056762512</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>0.271056347072729</v>
+        <v>0.271067131855498</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.2710313448514513</v>
+        <v>0.2710373804554943</v>
       </c>
       <c r="AK14" s="10" t="n">
-        <v>0.271062819860822</v>
+        <v>0.2710747437432402</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.2710028897205262</v>
+        <v>0.2710035495629999</v>
       </c>
       <c r="AM14" s="10" t="n">
-        <v>0.2709999984227078</v>
+        <v>0.2710001015608322</v>
       </c>
     </row>
     <row r="15">
@@ -1884,43 +1884,43 @@
         <v>4672633766</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>339933758</v>
+        <v>340988597</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>299831367</v>
+        <v>300762204</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>381674295</v>
+        <v>382873569</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>360107499</v>
+        <v>361226024</v>
       </c>
       <c r="AF15" s="7" t="n">
-        <v>422989417</v>
+        <v>424332217</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>396163571</v>
+        <v>397413731</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>430021399</v>
+        <v>431383197</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>444247006</v>
+        <v>445666408</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>409649024</v>
+        <v>410953212</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>444031645</v>
+        <v>445447984</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>402258901</v>
+        <v>403541189</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>421204589</v>
+        <v>422545391</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>4752112473</v>
+        <v>4767133723</v>
       </c>
     </row>
   </sheetData>

--- a/JPS_LE_Sales_Gen_FY2026-28.xlsx
+++ b/JPS_LE_Sales_Gen_FY2026-28.xlsx
@@ -1403,82 +1403,82 @@
         <v>268307438</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>13122370</v>
+        <v>13159607</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>13584362</v>
+        <v>13622911</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>16873095</v>
+        <v>16920976</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>15928334</v>
+        <v>15973534</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>17860284</v>
+        <v>17910966</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>17294476</v>
+        <v>17343552</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>18398744</v>
+        <v>18450954</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>16151667</v>
+        <v>16197500</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>16151667</v>
+        <v>16197500</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>16151667</v>
+        <v>16197500</v>
       </c>
       <c r="Y11" s="7" t="n">
-        <v>16151667</v>
+        <v>16197500</v>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>16151667</v>
+        <v>16197500</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>193820000</v>
+        <v>194370000</v>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>12656567</v>
+        <v>12865095</v>
       </c>
       <c r="AC11" s="7" t="n">
-        <v>13102160</v>
+        <v>13318030</v>
       </c>
       <c r="AD11" s="7" t="n">
-        <v>16274153</v>
+        <v>16542284</v>
       </c>
       <c r="AE11" s="7" t="n">
-        <v>15362928</v>
+        <v>15616046</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>17226300</v>
+        <v>17510119</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>16680577</v>
+        <v>16955404</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>17745647</v>
+        <v>18038022</v>
       </c>
       <c r="AI11" s="7" t="n">
-        <v>15578333</v>
+        <v>15835000</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>15578333</v>
+        <v>15835000</v>
       </c>
       <c r="AK11" s="7" t="n">
-        <v>15578333</v>
+        <v>15835000</v>
       </c>
       <c r="AL11" s="7" t="n">
-        <v>15578333</v>
+        <v>15835000</v>
       </c>
       <c r="AM11" s="7" t="n">
-        <v>15578333</v>
+        <v>15835000</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>186940000</v>
+        <v>190020000</v>
       </c>
     </row>
     <row r="12">
@@ -1527,82 +1527,82 @@
         <v>3281970498</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>241287212</v>
+        <v>241324450</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>227468930</v>
+        <v>227507478</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>265180986</v>
+        <v>265228866</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>257092538</v>
+        <v>257137737</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>288182829</v>
+        <v>288233511</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>286343514</v>
+        <v>286392590</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>312825498</v>
+        <v>312877708</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>309942837</v>
+        <v>309988671</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>300658011</v>
+        <v>300703844</v>
       </c>
       <c r="X12" s="9" t="n">
-        <v>309520786</v>
+        <v>309566619</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>305081081</v>
+        <v>305126915</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>302765778</v>
+        <v>302811611</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>3406350000</v>
+        <v>3406900000</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>246331768</v>
+        <v>246540296</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>232234952</v>
+        <v>232450822</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>270559411</v>
+        <v>270827541</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>262287917</v>
+        <v>262541035</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>293979359</v>
+        <v>294263177</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>292021482</v>
+        <v>292296309</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>318945199</v>
+        <v>319237574</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>316246982</v>
+        <v>316503649</v>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>306716866</v>
+        <v>306973532</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>315780174</v>
+        <v>316036840</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>311253220</v>
+        <v>311509887</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>308882671</v>
+        <v>309139338</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>3475240000</v>
+        <v>3478320000</v>
       </c>
     </row>
     <row r="13">
@@ -1669,10 +1669,10 @@
         <v>0.2606444</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>0.2903944000000001</v>
+        <v>0.2903944</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>0.2536443999999999</v>
+        <v>0.2536444</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>0.2910944</v>
@@ -1684,7 +1684,7 @@
         <v>0.2689944</v>
       </c>
       <c r="AB13" s="10" t="n">
-        <v>0.2775952900000001</v>
+        <v>0.27759529</v>
       </c>
       <c r="AC13" s="10" t="n">
         <v>0.22784529</v>
@@ -1711,7 +1711,7 @@
         <v>0.25364529</v>
       </c>
       <c r="AK13" s="10" t="n">
-        <v>0.2910952900000001</v>
+        <v>0.29109529</v>
       </c>
       <c r="AL13" s="10" t="n">
         <v>0.22869529</v>
@@ -1727,76 +1727,76 @@
         </is>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.270756418178832</v>
+        <v>0.2707564963259076</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>0.2694621680784696</v>
+        <v>0.269461800412616</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>0.2726761197823894</v>
+        <v>0.2726759910979907</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>0.272514247384364</v>
+        <v>0.272514143839467</v>
       </c>
       <c r="S14" s="10" t="n">
-        <v>0.2742976146694242</v>
+        <v>0.2742979479981406</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>0.2724846298658751</v>
+        <v>0.2724849776297297</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>0.2700226104841081</v>
+        <v>0.2700230138811037</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0.2728802379487836</v>
+        <v>0.2728806093583514</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>0.2723050394976059</v>
+        <v>0.272305224454467</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>0.2743841666241973</v>
+        <v>0.2743843285935077</v>
       </c>
       <c r="Y14" s="10" t="n">
-        <v>0.2709844374177692</v>
+        <v>0.2709845215451044</v>
       </c>
       <c r="Z14" s="10" t="n">
-        <v>0.2710000033313201</v>
+        <v>0.2710000578476282</v>
       </c>
       <c r="AB14" s="10" t="n">
-        <v>0.2710099090349518</v>
+        <v>0.271010295484347</v>
       </c>
       <c r="AC14" s="10" t="n">
-        <v>0.2709531031715005</v>
+        <v>0.2709513890123705</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.2709894891292186</v>
+        <v>0.2709892525327096</v>
       </c>
       <c r="AE14" s="10" t="n">
-        <v>0.2709939796164094</v>
+        <v>0.2709939186148568</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>0.2710583843781971</v>
+        <v>0.2710608798774421</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.2710488519537005</v>
+        <v>0.271050966491011</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.2710307056762512</v>
+        <v>0.27103211227549</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>0.271067131855498</v>
+        <v>0.2710697266252198</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.2710373804554943</v>
+        <v>0.2710389546485719</v>
       </c>
       <c r="AK14" s="10" t="n">
-        <v>0.2710747437432402</v>
+        <v>0.2710775408202913</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.2710035495629999</v>
+        <v>0.2710039683757329</v>
       </c>
       <c r="AM14" s="10" t="n">
-        <v>0.2710001015608322</v>
+        <v>0.2710004012860903</v>
       </c>
     </row>
     <row r="15">
@@ -1845,82 +1845,82 @@
         <v>4501741388</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>334005180</v>
+        <v>334056726</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>294589497</v>
+        <v>294639420</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>375261988</v>
+        <v>375329745</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>354070452</v>
+        <v>354132701</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>415964925</v>
+        <v>416038079</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>389686080</v>
+        <v>389752868</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>423105605</v>
+        <v>423176220</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>436781837</v>
+        <v>436846427</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>402834802</v>
+        <v>402896212</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>436617775</v>
+        <v>436682429</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>395538528</v>
+        <v>395597951</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>414177098</v>
+        <v>414239797</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>4672633766</v>
+        <v>4673388574</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>340988597</v>
+        <v>341277255</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>300762204</v>
+        <v>301041772</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>382873569</v>
+        <v>383253005</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>361226024</v>
+        <v>361574621</v>
       </c>
       <c r="AF15" s="7" t="n">
-        <v>424332217</v>
+        <v>424741883</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>397413731</v>
+        <v>397787745</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>431383197</v>
+        <v>431778643</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>445666408</v>
+        <v>446028112</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>410953212</v>
+        <v>411297106</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>445447984</v>
+        <v>445810045</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>403541189</v>
+        <v>403873959</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>422545391</v>
+        <v>422896506</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>4767133723</v>
+        <v>4771360651</v>
       </c>
     </row>
   </sheetData>

--- a/JPS_LE_Sales_Gen_FY2026-28.xlsx
+++ b/JPS_LE_Sales_Gen_FY2026-28.xlsx
@@ -1648,76 +1648,76 @@
         <v>0.2686969496197062</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.2775944</v>
+        <v>0.2775</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>0.2278444</v>
+        <v>0.2278</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>0.2933444</v>
+        <v>0.2934</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>0.2738944</v>
+        <v>0.2739</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>0.3071944</v>
+        <v>0.3072</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>0.2651944</v>
+        <v>0.2653000000000001</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>0.2606444</v>
+        <v>0.2756</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>0.2903944</v>
+        <v>0.2821</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>0.2536444</v>
+        <v>0.2535000000000001</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>0.2910944</v>
+        <v>0.2544999999999999</v>
       </c>
       <c r="Y13" s="10" t="n">
-        <v>0.2286944</v>
+        <v>0.2475</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>0.2689944</v>
+        <v>0.2834</v>
       </c>
       <c r="AB13" s="10" t="n">
-        <v>0.27759529</v>
+        <v>0.2777000000000001</v>
       </c>
       <c r="AC13" s="10" t="n">
-        <v>0.22784529</v>
+        <v>0.2281</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>0.29334529</v>
+        <v>0.2932999999999999</v>
       </c>
       <c r="AE13" s="10" t="n">
-        <v>0.27389529</v>
+        <v>0.2737999999999999</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>0.30719529</v>
+        <v>0.3071</v>
       </c>
       <c r="AG13" s="10" t="n">
-        <v>0.26519529</v>
+        <v>0.2651999999999999</v>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>0.26064529</v>
+        <v>0.2756000000000001</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>0.29039529</v>
+        <v>0.2821</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>0.25364529</v>
+        <v>0.2535000000000001</v>
       </c>
       <c r="AK13" s="10" t="n">
-        <v>0.29109529</v>
+        <v>0.2545</v>
       </c>
       <c r="AL13" s="10" t="n">
-        <v>0.22869529</v>
+        <v>0.2475</v>
       </c>
       <c r="AM13" s="10" t="n">
-        <v>0.26899529</v>
+        <v>0.2834</v>
       </c>
     </row>
     <row r="14">
@@ -1727,76 +1727,76 @@
         </is>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.2707564963259076</v>
+        <v>0.2707494393174217</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>0.269461800412616</v>
+        <v>0.2694519879643323</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>0.2726759910979907</v>
+        <v>0.272671015705942</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>0.272514143839467</v>
+        <v>0.2725096129283053</v>
       </c>
       <c r="S14" s="10" t="n">
-        <v>0.2742979479981406</v>
+        <v>0.2742939831176538</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>0.2724849776297297</v>
+        <v>0.2724899252840452</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>0.2700230138811037</v>
+        <v>0.2714231670550463</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0.2728806093583514</v>
+        <v>0.2734682315923941</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>0.272305224454467</v>
+        <v>0.2728788725807887</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>0.2743843285935077</v>
+        <v>0.2715978419491913</v>
       </c>
       <c r="Y14" s="10" t="n">
-        <v>0.2709845215451044</v>
+        <v>0.2697431846747227</v>
       </c>
       <c r="Z14" s="10" t="n">
-        <v>0.2710000578476282</v>
+        <v>0.2710656963309189</v>
       </c>
       <c r="AB14" s="10" t="n">
-        <v>0.271010295484347</v>
+        <v>0.2710903322121693</v>
       </c>
       <c r="AC14" s="10" t="n">
-        <v>0.2709513890123705</v>
+        <v>0.2710494051677043</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.2709892525327096</v>
+        <v>0.2710787007428112</v>
       </c>
       <c r="AE14" s="10" t="n">
-        <v>0.2709939186148568</v>
+        <v>0.2710754477737373</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>0.2710608798774421</v>
+        <v>0.2711326946188875</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.271050966491011</v>
+        <v>0.2711144020746904</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.27103211227549</v>
+        <v>0.271122730910779</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>0.2710697266252198</v>
+        <v>0.2711437592533857</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.2710389546485719</v>
+        <v>0.2711125344491949</v>
       </c>
       <c r="AK14" s="10" t="n">
-        <v>0.2710775408202913</v>
+        <v>0.2710822090638449</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.2710039683757329</v>
+        <v>0.2710402113411011</v>
       </c>
       <c r="AM14" s="10" t="n">
-        <v>0.2710004012860903</v>
+        <v>0.2710630832469147</v>
       </c>
     </row>
     <row r="15">
@@ -1845,82 +1845,82 @@
         <v>4501741388</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>334056726</v>
+        <v>334013079</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>294639420</v>
+        <v>294622479</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>375329745</v>
+        <v>375359278</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>354132701</v>
+        <v>354135432</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>416038079</v>
+        <v>416041442</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>389752868</v>
+        <v>389808888</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>423176220</v>
+        <v>431912904</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>436846427</v>
+        <v>431799235</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>402896212</v>
+        <v>402818277</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>436682429</v>
+        <v>415246974</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>395597951</v>
+        <v>405484272</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>414239797</v>
+        <v>422567138</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>4673388574</v>
+        <v>4673809399</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>341277255</v>
+        <v>341326729</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>301041772</v>
+        <v>301141109</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>383253005</v>
+        <v>383228444</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>361574621</v>
+        <v>361527176</v>
       </c>
       <c r="AF15" s="7" t="n">
-        <v>424741883</v>
+        <v>424683471</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>397787745</v>
+        <v>397790295</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>431778643</v>
+        <v>440692399</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>446028112</v>
+        <v>440874285</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>411297106</v>
+        <v>411217056</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>445810045</v>
+        <v>423926010</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>403873959</v>
+        <v>413966627</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>422896506</v>
+        <v>431397346</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>4771360651</v>
+        <v>4771770945</v>
       </c>
     </row>
   </sheetData>
